--- a/docs/sap490/generated/Functional_Test_IDTS_SAP01_vi_v0.2.xlsx
+++ b/docs/sap490/generated/Functional_Test_IDTS_SAP01_vi_v0.2.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="151">
   <si>
     <t xml:space="preserve">Kiểm thử chức năng</t>
   </si>
@@ -266,15 +266,18 @@
     <t xml:space="preserve">Điều kiện trước: Tester đã đăng nhập; có ít nhất một bug tương tự và một bug không liên quan.
 Dữ liệu: Mô tả lỗi login mới và classification context.
 Dự kiến: Candidate liên quan hiển thị dạng gợi ý; bỏ qua không đổi dữ liệu hoặc chặn create.
-Thực tế / điều kiện sau: Chưa chạy | Không có quan hệ duplicate tự động.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA. API v? h?p tho?i Fiori tr? g?i ? tr?ng l?p ch? ?? review, bao ph? tr?ng th?i kh?ng c? k?t qu? v? kh?ng thay ??i d? li?u workflow c?a Bug. | Không có quan hệ duplicate tự động.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pending</t>
+    <t xml:space="preserve">IDTS-100 automated acceptance under DonHV</t>
   </si>
   <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: None | Chưa chạy mới duplicate review UI/API trong remediation này.</t>
+    <t xml:space="preserve">2026-07-24T20:42:48+07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lệnh: node scripts/qa/test-idts100-shared-qa-lifecycle.js and focused browser/API harnesses
+Bằng chứng: docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json
+Defect / giới hạn: None | Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-CLASS-ASSIGN-001</t>
@@ -288,12 +291,12 @@
     <t xml:space="preserve">Điều kiện trước: Có classification pair và Developer Responsibility active.
 Dữ liệu: Application Component=Bug Management; Defect Category=Fiori/UI5; một Developer phù hợp và một không phù hợp.
 Dự kiến: Chỉ candidate active có responsibility được chọn; bug lưu ở Assigned và ownership còn sau reload.
-Thực tế / điều kiện sau: Chưa chạy | Developer được assign là technical owner.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA. Mapping ph?n lo?i active ???c ch?p nh?n, Developer ph? h?p ???c assign, Developer t? assign qua API b? ch?n, v? Smart Assign v?n gi? quy?t ??nh th? c?ng. | Developer được assign là technical owner.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: IDTS-56 | Cần evidence browser và persistence mới.</t>
+    <t xml:space="preserve">Lệnh: node scripts/qa/test-idts100-shared-qa-lifecycle.js and focused browser/API harnesses
+Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json
+Defect / giới hạn: IDTS-56 | Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-PENDING-001</t>
@@ -307,12 +310,12 @@
     <t xml:space="preserve">Điều kiện trước: Tester đã đăng nhập và mọi field bắt buộc hợp lệ.
 Dữ liệu: Bug hợp lệ nhưng không chọn assignee.
 Dự kiến: Bug ở Pending Assignment; không Developer nào được tự chọn; PM/Tester queue nhận action tiếp theo.
-Thực tế / điều kiện sau: Chưa chạy | Bug chờ assignment rõ ràng.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA. Activate draft h?p l? kh?ng c? assignee t?o tr?ng th?i PENDING_ASSIGNMENT, kh?ng c? assignee v? PM l? vai tr? x? l? ti?p theo. | Bug chờ assignment rõ ràng.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: None | Cần evidence create/reload mới.</t>
+    <t xml:space="preserve">Lệnh: node scripts/qa/test-idts100-shared-qa-lifecycle.js and focused browser/API harnesses
+Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json
+Defect / giới hạn: None | Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-REASSIGN-001</t>
@@ -326,12 +329,7 @@
     <t xml:space="preserve">Điều kiện trước: Có bug đã assign và Developer phù hợp thứ hai.
 Dữ liệu: Lý do: cân bằng workload.
 Dự kiến: Chỉ còn một assignee; history có actor, owner cũ/mới, lý do và timestamp.
-Thực tế / điều kiện sau: Chưa chạy | Developer mới là technical owner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: None | Quyền PM reassign trực tiếp vẫn phụ thuộc decision đã ghi; chạy bằng role runtime hiện cho phép.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA. Bug ?i t? Rejected v? Pending Assignment, x?a assignee, ???c assign l?i v? gi? ??ng action type trong history. | Developer mới là technical owner.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-DEV-INFO-001</t>
@@ -345,12 +343,12 @@
     <t xml:space="preserve">Điều kiện trước: Bug đã assign; có account Developer được assign và không được assign.
 Dữ liệu: Lý do: thiếu phiên bản browser và bước tái hiện chính xác.
 Dự kiến: Sai role/owner và reason rỗng bị chặn; action hợp lệ set Need More Information và Tester action owner cùng audit/notification.
-Thực tế / điều kiện sau: Chưa chạy | Tester phải bổ sung thông tin và resubmit.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA. Developer ???c assign y?u c?u th?m th?ng tin, reason r?ng tr? 400 v? Tester resubmit Bug v? ??ng Developer. | Tester phải bổ sung thông tin và resubmit.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: None | Cần evidence role matrix và reload mới.</t>
+    <t xml:space="preserve">Lệnh: node scripts/qa/test-idts100-shared-qa-lifecycle.js and focused browser/API harnesses
+Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md
+Defect / giới hạn: None | Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-REJECT-001</t>
@@ -364,12 +362,7 @@
     <t xml:space="preserve">Điều kiện trước: Bug đã assign nhưng classification hoặc owner không phù hợp.
 Dữ liệu: Lý do: component là Notification, không phải Dashboard.
 Dự kiến: Reason rỗng bị chặn; rejection hợp lệ ghi follow-up; sau sửa rời Rejected qua Assigned hoặc Pending Assignment, không đi thẳng Need More Information.
-Thực tế / điều kiện sau: Chưa chạy | Bug có technical/queue owner tiếp theo rõ ràng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: None | Cần evidence lifecycle UI/API đầy đủ.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA. Developer ???c assign reject k?m l? do; PM ??a Bug v? h?ng ??i assignment v? ho?n t?t correction follow-up b?ng reassign. | Bug có technical/queue owner tiếp theo rõ ràng.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-LIFECYCLE-001</t>
@@ -383,12 +376,7 @@
     <t xml:space="preserve">Điều kiện trước: Bug đang In Progress và tái hiện được.
 Dữ liệu: Resolution note cùng một observation retest pass và một fail.
 Dự kiến: Pass đến Closed; fail đến Reopened; note bắt buộc, owner và audit nhất quán sau reload.
-Thực tế / điều kiện sau: Chưa chạy | Closed không có next processor; Reopened quay lại xử lý active.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: None | Chưa chạy mới full lifecycle trong remediation này.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA v?i session PM, Tester v? Developer: assign, review, progress, y?u c?u th?ng tin, resubmit, resolve, retest, close, reopen, reject v? reassign ??u persist c?ng history ch?nh x?c v? notification side effect. | Closed không có next processor; Reopened quay lại xử lý active.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-COMMENT-001</t>
@@ -424,12 +412,12 @@
     <t xml:space="preserve">Điều kiện trước: Tester đã đăng nhập, có bug và file evidence nhỏ được phép.
 Dữ liệu: File text/image nhỏ, biến thể MIME không cho phép và file vượt giới hạn.
 Dự kiến: Evidence hợp lệ persist và download được; biến thể sai bị chặn; delete dọn storage và ghi history.
-Thực tế / điều kiện sau: Chưa chạy | Không còn attachment mồ côi.</t>
+Thực tế / điều kiện sau: ??t tr?n Render Shared QA. Hai file ch?n tr??c khi save ???c upload sau activation, download c? SHA-256 kh?p, c?n sau redeploy; m?t attachment ???c x?a v? l?n download sau tr? 404. | Không còn attachment mồ côi.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lệnh: npm run qa:comments-attachments:http
-Bằng chứng: scripts/qa/test-comments-attachments.ps1
-Defect / giới hạn: IDTS-55 | Command HTTP bắt buộc chưa chạy trong remediation; suite comments programmatic chỉ in note attachment.</t>
+    <t xml:space="preserve">Lệnh: npm run qa:idts73:browser + supported OData delete verification
+Bằng chứng: docs/pm/evidence/idts-100/shared-qa-attachments/idts73-create-attachments-browser.json, docs/pm/evidence/idts-100/shared-qa-attachments/delete-verification-20260724.md
+Defect / giới hạn: IDTS-55 | Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng.</t>
   </si>
   <si>
     <t xml:space="preserve">FT-NOTIF-001</t>
@@ -487,12 +475,12 @@
     <t xml:space="preserve">Điều kiện trước: User đã đăng nhập; có mode AI disabled và suggestion có kiểm soát.
 Dữ liệu: Suggestion similar/classification/handoff với biến thể safe và malformed.
 Dự kiến: Suggestion không tự đổi assignment, classification hoặc lifecycle; workflow bình thường vẫn dùng được.
-Thực tế / điều kiện sau: Chưa chạy | Bug không đổi trừ khi user có quyền thực hiện action bình thường riêng.</t>
+Thực tế / điều kiện sau: ??t acceptance khi provider b? t?t tr?n Render Shared QA. Similar Bugs, Classification, Handoff Summary v? Smart Assignment ??u ch? ?? review, an to?n, hi?n th? tr?n browser v? kh?ng thay ??i workflow. OpenAI live v?n NOT ACCEPTED theo quy?t ??nh. | Bug không đổi trừ khi user có quyền thực hiện action bình thường riêng.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lệnh: N/A
-Bằng chứng: N/A
-Defect / giới hạn: IDTS-78 | REG-AI-20260723 chỉ chứng minh provider safety, không phải full business flow human-review này.</t>
+    <t xml:space="preserve">Lệnh: node scripts/qa/test-idts100-shared-qa-lifecycle.js and focused browser/API harnesses
+Bằng chứng: docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json
+Defect / giới hạn: IDTS-78 | Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng.</t>
   </si>
   <si>
     <t xml:space="preserve">Run ID / lệnh chính xác</t>
@@ -5481,24 +5469,28 @@
       <c r="AU12" s="53"/>
       <c r="AV12" s="53"/>
       <c r="AW12" s="53"/>
-      <c r="AX12" s="54"/>
+      <c r="AX12" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY12" s="54"/>
       <c r="AZ12" s="54"/>
       <c r="BA12" s="54"/>
       <c r="BB12" s="54"/>
       <c r="BC12" s="54"/>
-      <c r="BD12" s="55"/>
+      <c r="BD12" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE12" s="55"/>
       <c r="BF12" s="55"/>
       <c r="BG12" s="55"/>
       <c r="BH12" s="55"/>
       <c r="BI12" s="55"/>
       <c r="BJ12" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK12" s="54"/>
       <c r="BL12" s="56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BM12" s="56"/>
       <c r="BN12" s="56"/>
@@ -5514,12 +5506,12 @@
     <row r="13" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="43"/>
       <c r="B13" s="57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="57"/>
       <c r="D13" s="57"/>
       <c r="E13" s="53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="53"/>
       <c r="G13" s="53"/>
@@ -5541,7 +5533,7 @@
       <c r="W13" s="53"/>
       <c r="X13" s="53"/>
       <c r="Y13" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z13" s="53"/>
       <c r="AA13" s="53"/>
@@ -5567,24 +5559,28 @@
       <c r="AU13" s="53"/>
       <c r="AV13" s="53"/>
       <c r="AW13" s="53"/>
-      <c r="AX13" s="54"/>
+      <c r="AX13" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY13" s="54"/>
       <c r="AZ13" s="54"/>
       <c r="BA13" s="54"/>
       <c r="BB13" s="54"/>
       <c r="BC13" s="54"/>
-      <c r="BD13" s="55"/>
+      <c r="BD13" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE13" s="55"/>
       <c r="BF13" s="55"/>
       <c r="BG13" s="55"/>
       <c r="BH13" s="55"/>
       <c r="BI13" s="55"/>
       <c r="BJ13" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK13" s="54"/>
       <c r="BL13" s="56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BM13" s="56"/>
       <c r="BN13" s="56"/>
@@ -5600,12 +5596,12 @@
     <row r="14" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="43"/>
       <c r="B14" s="51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F14" s="52"/>
       <c r="G14" s="52"/>
@@ -5627,7 +5623,7 @@
       <c r="W14" s="52"/>
       <c r="X14" s="52"/>
       <c r="Y14" s="52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z14" s="52"/>
       <c r="AA14" s="52"/>
@@ -5653,24 +5649,28 @@
       <c r="AU14" s="52"/>
       <c r="AV14" s="52"/>
       <c r="AW14" s="52"/>
-      <c r="AX14" s="54"/>
+      <c r="AX14" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY14" s="54"/>
       <c r="AZ14" s="54"/>
       <c r="BA14" s="54"/>
       <c r="BB14" s="54"/>
       <c r="BC14" s="54"/>
-      <c r="BD14" s="55"/>
+      <c r="BD14" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE14" s="55"/>
       <c r="BF14" s="55"/>
       <c r="BG14" s="55"/>
       <c r="BH14" s="55"/>
       <c r="BI14" s="55"/>
       <c r="BJ14" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK14" s="54"/>
       <c r="BL14" s="56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BM14" s="56"/>
       <c r="BN14" s="56"/>
@@ -5686,12 +5686,12 @@
     <row r="15" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="43"/>
       <c r="B15" s="57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="57"/>
       <c r="D15" s="57"/>
       <c r="E15" s="53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" s="53"/>
       <c r="G15" s="53"/>
@@ -5713,7 +5713,7 @@
       <c r="W15" s="53"/>
       <c r="X15" s="53"/>
       <c r="Y15" s="53" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z15" s="53"/>
       <c r="AA15" s="53"/>
@@ -5739,24 +5739,28 @@
       <c r="AU15" s="53"/>
       <c r="AV15" s="53"/>
       <c r="AW15" s="53"/>
-      <c r="AX15" s="54"/>
+      <c r="AX15" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY15" s="54"/>
       <c r="AZ15" s="54"/>
       <c r="BA15" s="54"/>
       <c r="BB15" s="54"/>
       <c r="BC15" s="54"/>
-      <c r="BD15" s="55"/>
+      <c r="BD15" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE15" s="55"/>
       <c r="BF15" s="55"/>
       <c r="BG15" s="55"/>
       <c r="BH15" s="55"/>
       <c r="BI15" s="55"/>
       <c r="BJ15" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK15" s="54"/>
       <c r="BL15" s="56" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="BM15" s="56"/>
       <c r="BN15" s="56"/>
@@ -5825,20 +5829,24 @@
       <c r="AU16" s="53"/>
       <c r="AV16" s="53"/>
       <c r="AW16" s="53"/>
-      <c r="AX16" s="54"/>
+      <c r="AX16" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY16" s="54"/>
       <c r="AZ16" s="54"/>
       <c r="BA16" s="54"/>
       <c r="BB16" s="54"/>
       <c r="BC16" s="54"/>
-      <c r="BD16" s="55"/>
+      <c r="BD16" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE16" s="55"/>
       <c r="BF16" s="55"/>
       <c r="BG16" s="55"/>
       <c r="BH16" s="55"/>
       <c r="BI16" s="55"/>
       <c r="BJ16" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK16" s="54"/>
       <c r="BL16" s="56" t="s">
@@ -5911,24 +5919,28 @@
       <c r="AU17" s="53"/>
       <c r="AV17" s="53"/>
       <c r="AW17" s="53"/>
-      <c r="AX17" s="54"/>
+      <c r="AX17" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY17" s="54"/>
       <c r="AZ17" s="54"/>
       <c r="BA17" s="54"/>
       <c r="BB17" s="54"/>
       <c r="BC17" s="54"/>
-      <c r="BD17" s="55"/>
+      <c r="BD17" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE17" s="55"/>
       <c r="BF17" s="55"/>
       <c r="BG17" s="55"/>
       <c r="BH17" s="55"/>
       <c r="BI17" s="55"/>
       <c r="BJ17" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK17" s="54"/>
       <c r="BL17" s="56" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="BM17" s="56"/>
       <c r="BN17" s="56"/>
@@ -5944,12 +5956,12 @@
     <row r="18" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="43"/>
       <c r="B18" s="57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" s="57"/>
       <c r="D18" s="57"/>
       <c r="E18" s="53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -5971,7 +5983,7 @@
       <c r="W18" s="53"/>
       <c r="X18" s="53"/>
       <c r="Y18" s="53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z18" s="53"/>
       <c r="AA18" s="53"/>
@@ -5997,24 +6009,28 @@
       <c r="AU18" s="53"/>
       <c r="AV18" s="53"/>
       <c r="AW18" s="53"/>
-      <c r="AX18" s="54"/>
+      <c r="AX18" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY18" s="54"/>
       <c r="AZ18" s="54"/>
       <c r="BA18" s="54"/>
       <c r="BB18" s="54"/>
       <c r="BC18" s="54"/>
-      <c r="BD18" s="55"/>
+      <c r="BD18" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE18" s="55"/>
       <c r="BF18" s="55"/>
       <c r="BG18" s="55"/>
       <c r="BH18" s="55"/>
       <c r="BI18" s="55"/>
       <c r="BJ18" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK18" s="54"/>
       <c r="BL18" s="56" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="BM18" s="56"/>
       <c r="BN18" s="56"/>
@@ -6030,12 +6046,12 @@
     <row r="19" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="43"/>
       <c r="B19" s="51" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F19" s="52"/>
       <c r="G19" s="52"/>
@@ -6057,7 +6073,7 @@
       <c r="W19" s="52"/>
       <c r="X19" s="52"/>
       <c r="Y19" s="53" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Z19" s="53"/>
       <c r="AA19" s="53"/>
@@ -6092,7 +6108,7 @@
       <c r="BB19" s="54"/>
       <c r="BC19" s="54"/>
       <c r="BD19" s="55" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="BE19" s="55"/>
       <c r="BF19" s="55"/>
@@ -6104,7 +6120,7 @@
       </c>
       <c r="BK19" s="54"/>
       <c r="BL19" s="58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="BM19" s="58"/>
       <c r="BN19" s="58"/>
@@ -6120,12 +6136,12 @@
     <row r="20" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="43"/>
       <c r="B20" s="57" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C20" s="57"/>
       <c r="D20" s="57"/>
       <c r="E20" s="53" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53"/>
@@ -6147,7 +6163,7 @@
       <c r="W20" s="53"/>
       <c r="X20" s="53"/>
       <c r="Y20" s="53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Z20" s="53"/>
       <c r="AA20" s="53"/>
@@ -6173,24 +6189,28 @@
       <c r="AU20" s="53"/>
       <c r="AV20" s="53"/>
       <c r="AW20" s="53"/>
-      <c r="AX20" s="54"/>
+      <c r="AX20" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY20" s="54"/>
       <c r="AZ20" s="54"/>
       <c r="BA20" s="54"/>
       <c r="BB20" s="54"/>
       <c r="BC20" s="54"/>
-      <c r="BD20" s="55"/>
+      <c r="BD20" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE20" s="55"/>
       <c r="BF20" s="55"/>
       <c r="BG20" s="55"/>
       <c r="BH20" s="55"/>
       <c r="BI20" s="55"/>
       <c r="BJ20" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK20" s="54"/>
       <c r="BL20" s="58" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="BM20" s="58"/>
       <c r="BN20" s="58"/>
@@ -6206,12 +6226,12 @@
     <row r="21" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="43"/>
       <c r="B21" s="57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21" s="57"/>
       <c r="D21" s="57"/>
       <c r="E21" s="53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53"/>
@@ -6233,7 +6253,7 @@
       <c r="W21" s="53"/>
       <c r="X21" s="53"/>
       <c r="Y21" s="53" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Z21" s="53"/>
       <c r="AA21" s="53"/>
@@ -6268,7 +6288,7 @@
       <c r="BB21" s="54"/>
       <c r="BC21" s="54"/>
       <c r="BD21" s="55" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="BE21" s="55"/>
       <c r="BF21" s="55"/>
@@ -6280,7 +6300,7 @@
       </c>
       <c r="BK21" s="54"/>
       <c r="BL21" s="58" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="BM21" s="58"/>
       <c r="BN21" s="58"/>
@@ -6296,12 +6316,12 @@
     <row r="22" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="43"/>
       <c r="B22" s="57" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C22" s="57"/>
       <c r="D22" s="57"/>
       <c r="E22" s="53" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53"/>
@@ -6323,7 +6343,7 @@
       <c r="W22" s="53"/>
       <c r="X22" s="53"/>
       <c r="Y22" s="53" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Z22" s="53"/>
       <c r="AA22" s="53"/>
@@ -6358,7 +6378,7 @@
       <c r="BB22" s="54"/>
       <c r="BC22" s="54"/>
       <c r="BD22" s="55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="BE22" s="55"/>
       <c r="BF22" s="55"/>
@@ -6370,7 +6390,7 @@
       </c>
       <c r="BK22" s="54"/>
       <c r="BL22" s="58" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BM22" s="58"/>
       <c r="BN22" s="58"/>
@@ -6386,12 +6406,12 @@
     <row r="23" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="43"/>
       <c r="B23" s="57" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C23" s="57"/>
       <c r="D23" s="57"/>
       <c r="E23" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53"/>
@@ -6413,7 +6433,7 @@
       <c r="W23" s="53"/>
       <c r="X23" s="53"/>
       <c r="Y23" s="53" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Z23" s="53"/>
       <c r="AA23" s="53"/>
@@ -6439,24 +6459,28 @@
       <c r="AU23" s="53"/>
       <c r="AV23" s="53"/>
       <c r="AW23" s="53"/>
-      <c r="AX23" s="54"/>
+      <c r="AX23" s="54" t="s">
+        <v>61</v>
+      </c>
       <c r="AY23" s="54"/>
       <c r="AZ23" s="54"/>
       <c r="BA23" s="54"/>
       <c r="BB23" s="54"/>
       <c r="BC23" s="54"/>
-      <c r="BD23" s="55"/>
+      <c r="BD23" s="55" t="s">
+        <v>62</v>
+      </c>
       <c r="BE23" s="55"/>
       <c r="BF23" s="55"/>
       <c r="BG23" s="55"/>
       <c r="BH23" s="55"/>
       <c r="BI23" s="55"/>
       <c r="BJ23" s="54" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="BK23" s="54"/>
       <c r="BL23" s="58" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="BM23" s="58"/>
       <c r="BN23" s="58"/>
@@ -7835,7 +7859,7 @@
     <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="44"/>
       <c r="B4" s="60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -7847,7 +7871,7 @@
       <c r="J4" s="60"/>
       <c r="K4" s="60"/>
       <c r="L4" s="60" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M4" s="60"/>
       <c r="N4" s="60"/>
@@ -7889,7 +7913,7 @@
       <c r="AV4" s="60"/>
       <c r="AW4" s="60"/>
       <c r="AX4" s="60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AY4" s="60"/>
       <c r="AZ4" s="60"/>
@@ -7898,7 +7922,7 @@
       <c r="BC4" s="60"/>
       <c r="BD4" s="60"/>
       <c r="BE4" s="60" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BF4" s="60"/>
       <c r="BG4" s="60"/>
@@ -7907,7 +7931,7 @@
       <c r="BJ4" s="60"/>
       <c r="BK4" s="60"/>
       <c r="BL4" s="60" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="BM4" s="60"/>
       <c r="BN4" s="60"/>
@@ -8135,7 +8159,7 @@
     <row r="8" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="43"/>
       <c r="B8" s="64" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C8" s="64"/>
       <c r="D8" s="64"/>
@@ -8147,7 +8171,7 @@
       <c r="J8" s="64"/>
       <c r="K8" s="64"/>
       <c r="L8" s="65" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M8" s="65"/>
       <c r="N8" s="65"/>
@@ -8198,7 +8222,7 @@
       <c r="BC8" s="66"/>
       <c r="BD8" s="66"/>
       <c r="BE8" s="66" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="BF8" s="66"/>
       <c r="BG8" s="66"/>
@@ -8207,7 +8231,7 @@
       <c r="BJ8" s="66"/>
       <c r="BK8" s="66"/>
       <c r="BL8" s="65" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BM8" s="65"/>
       <c r="BN8" s="65"/>
@@ -8219,7 +8243,7 @@
     <row r="9" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="43"/>
       <c r="B9" s="65" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="65"/>
       <c r="D9" s="65"/>
@@ -8231,7 +8255,7 @@
       <c r="J9" s="65"/>
       <c r="K9" s="65"/>
       <c r="L9" s="65" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M9" s="65"/>
       <c r="N9" s="65"/>
@@ -8273,7 +8297,7 @@
       <c r="AV9" s="66"/>
       <c r="AW9" s="66"/>
       <c r="AX9" s="66" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AY9" s="66"/>
       <c r="AZ9" s="66"/>
@@ -8282,7 +8306,7 @@
       <c r="BC9" s="66"/>
       <c r="BD9" s="66"/>
       <c r="BE9" s="66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="BF9" s="66"/>
       <c r="BG9" s="66"/>
@@ -8291,7 +8315,7 @@
       <c r="BJ9" s="66"/>
       <c r="BK9" s="66"/>
       <c r="BL9" s="65" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="BM9" s="65"/>
       <c r="BN9" s="65"/>
@@ -8303,7 +8327,7 @@
     <row r="10" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="43"/>
       <c r="B10" s="65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C10" s="65"/>
       <c r="D10" s="65"/>
@@ -8315,7 +8339,7 @@
       <c r="J10" s="65"/>
       <c r="K10" s="65"/>
       <c r="L10" s="65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M10" s="65"/>
       <c r="N10" s="65"/>
@@ -8357,7 +8381,7 @@
       <c r="AV10" s="66"/>
       <c r="AW10" s="66"/>
       <c r="AX10" s="66" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AY10" s="66"/>
       <c r="AZ10" s="66"/>
@@ -8366,7 +8390,7 @@
       <c r="BC10" s="66"/>
       <c r="BD10" s="66"/>
       <c r="BE10" s="66" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="BF10" s="66"/>
       <c r="BG10" s="66"/>
@@ -8375,7 +8399,7 @@
       <c r="BJ10" s="66"/>
       <c r="BK10" s="66"/>
       <c r="BL10" s="65" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="BM10" s="65"/>
       <c r="BN10" s="65"/>
@@ -8387,7 +8411,7 @@
     <row r="11" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="43"/>
       <c r="B11" s="65" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="65"/>
@@ -8399,7 +8423,7 @@
       <c r="J11" s="65"/>
       <c r="K11" s="65"/>
       <c r="L11" s="65" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M11" s="65"/>
       <c r="N11" s="65"/>
@@ -8450,7 +8474,7 @@
       <c r="BC11" s="66"/>
       <c r="BD11" s="66"/>
       <c r="BE11" s="66" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BF11" s="66"/>
       <c r="BG11" s="66"/>
@@ -8459,7 +8483,7 @@
       <c r="BJ11" s="66"/>
       <c r="BK11" s="66"/>
       <c r="BL11" s="65" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BM11" s="65"/>
       <c r="BN11" s="65"/>
@@ -8471,7 +8495,7 @@
     <row r="12" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="43"/>
       <c r="B12" s="65" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C12" s="65"/>
       <c r="D12" s="65"/>
@@ -8483,7 +8507,7 @@
       <c r="J12" s="65"/>
       <c r="K12" s="65"/>
       <c r="L12" s="65" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M12" s="65"/>
       <c r="N12" s="65"/>
@@ -8525,7 +8549,7 @@
       <c r="AV12" s="66"/>
       <c r="AW12" s="66"/>
       <c r="AX12" s="66" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AY12" s="66"/>
       <c r="AZ12" s="66"/>
@@ -8534,7 +8558,7 @@
       <c r="BC12" s="66"/>
       <c r="BD12" s="66"/>
       <c r="BE12" s="66" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BF12" s="66"/>
       <c r="BG12" s="66"/>
@@ -8543,7 +8567,7 @@
       <c r="BJ12" s="66"/>
       <c r="BK12" s="66"/>
       <c r="BL12" s="65" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="BM12" s="65"/>
       <c r="BN12" s="65"/>
@@ -8555,7 +8579,7 @@
     <row r="13" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="43"/>
       <c r="B13" s="65" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="65"/>
@@ -8567,7 +8591,7 @@
       <c r="J13" s="65"/>
       <c r="K13" s="65"/>
       <c r="L13" s="65" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M13" s="65"/>
       <c r="N13" s="65"/>
@@ -8609,7 +8633,7 @@
       <c r="AV13" s="66"/>
       <c r="AW13" s="66"/>
       <c r="AX13" s="66" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AY13" s="66"/>
       <c r="AZ13" s="66"/>
@@ -8618,7 +8642,7 @@
       <c r="BC13" s="66"/>
       <c r="BD13" s="66"/>
       <c r="BE13" s="66" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="BF13" s="66"/>
       <c r="BG13" s="66"/>
@@ -8627,7 +8651,7 @@
       <c r="BJ13" s="66"/>
       <c r="BK13" s="66"/>
       <c r="BL13" s="65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="BM13" s="65"/>
       <c r="BN13" s="65"/>
@@ -13289,7 +13313,7 @@
       <c r="J3" s="47"/>
       <c r="K3" s="47"/>
       <c r="L3" s="47" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M3" s="47"/>
       <c r="N3" s="47"/>
@@ -13649,7 +13673,7 @@
     <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="43"/>
       <c r="B8" s="66" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C8" s="66"/>
       <c r="D8" s="66"/>
@@ -13661,7 +13685,7 @@
       <c r="J8" s="66"/>
       <c r="K8" s="66"/>
       <c r="L8" s="65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M8" s="65"/>
       <c r="N8" s="65"/>
@@ -13712,7 +13736,7 @@
       <c r="BC8" s="67"/>
       <c r="BD8" s="67"/>
       <c r="BE8" s="66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BF8" s="66"/>
       <c r="BG8" s="66"/>
@@ -13721,7 +13745,7 @@
       <c r="BJ8" s="66"/>
       <c r="BK8" s="66"/>
       <c r="BL8" s="65" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="BM8" s="65"/>
       <c r="BN8" s="65"/>
@@ -13733,7 +13757,7 @@
     <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="43"/>
       <c r="B9" s="66" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C9" s="66"/>
       <c r="D9" s="66"/>
@@ -13745,7 +13769,7 @@
       <c r="J9" s="66"/>
       <c r="K9" s="66"/>
       <c r="L9" s="65" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M9" s="65"/>
       <c r="N9" s="65"/>
@@ -13796,7 +13820,7 @@
       <c r="BC9" s="67"/>
       <c r="BD9" s="67"/>
       <c r="BE9" s="66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BF9" s="66"/>
       <c r="BG9" s="66"/>
@@ -13805,7 +13829,7 @@
       <c r="BJ9" s="66"/>
       <c r="BK9" s="66"/>
       <c r="BL9" s="65" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="BM9" s="65"/>
       <c r="BN9" s="65"/>
@@ -13817,7 +13841,7 @@
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="43"/>
       <c r="B10" s="66" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C10" s="66"/>
       <c r="D10" s="66"/>
@@ -13829,7 +13853,7 @@
       <c r="J10" s="66"/>
       <c r="K10" s="66"/>
       <c r="L10" s="65" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M10" s="65"/>
       <c r="N10" s="65"/>
@@ -13880,7 +13904,7 @@
       <c r="BC10" s="67"/>
       <c r="BD10" s="67"/>
       <c r="BE10" s="66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BF10" s="66"/>
       <c r="BG10" s="66"/>
@@ -13889,7 +13913,7 @@
       <c r="BJ10" s="66"/>
       <c r="BK10" s="66"/>
       <c r="BL10" s="65" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="BM10" s="65"/>
       <c r="BN10" s="65"/>
@@ -13901,7 +13925,7 @@
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="43"/>
       <c r="B11" s="66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="66"/>
@@ -13913,7 +13937,7 @@
       <c r="J11" s="66"/>
       <c r="K11" s="66"/>
       <c r="L11" s="65" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M11" s="65"/>
       <c r="N11" s="65"/>
@@ -13964,7 +13988,7 @@
       <c r="BC11" s="67"/>
       <c r="BD11" s="67"/>
       <c r="BE11" s="66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BF11" s="66"/>
       <c r="BG11" s="66"/>
@@ -13973,7 +13997,7 @@
       <c r="BJ11" s="66"/>
       <c r="BK11" s="66"/>
       <c r="BL11" s="65" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="BM11" s="65"/>
       <c r="BN11" s="65"/>
@@ -13985,7 +14009,7 @@
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="43"/>
       <c r="B12" s="66" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="66"/>
@@ -13997,7 +14021,7 @@
       <c r="J12" s="66"/>
       <c r="K12" s="66"/>
       <c r="L12" s="65" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M12" s="65"/>
       <c r="N12" s="65"/>
@@ -14048,7 +14072,7 @@
       <c r="BC12" s="67"/>
       <c r="BD12" s="67"/>
       <c r="BE12" s="66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BF12" s="66"/>
       <c r="BG12" s="66"/>
@@ -14057,7 +14081,7 @@
       <c r="BJ12" s="66"/>
       <c r="BK12" s="66"/>
       <c r="BL12" s="65" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="BM12" s="65"/>
       <c r="BN12" s="65"/>
